--- a/resultados_clasificadores/naive_bayes_modelo2.xlsx
+++ b/resultados_clasificadores/naive_bayes_modelo2.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priors2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medias2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Varianzas2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Priors2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Medias2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Varianzas2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,12 +490,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>EDA_SCR_count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>EDA_SCR_count</t>
+          <t>EDA_Phasic_AUC</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -515,10 +515,10 @@
         <v>0.096202645907012</v>
       </c>
       <c r="D2" t="n">
-        <v>2189.234693877551</v>
+        <v>-0.03852068755220759</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03852068755220759</v>
+        <v>-0.09596117372763521</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
         <v>-0.4250328589123709</v>
       </c>
       <c r="D3" t="n">
-        <v>2963.368421052632</v>
+        <v>0.490311701763354</v>
       </c>
       <c r="E3" t="n">
-        <v>0.490311701763354</v>
+        <v>0.3795169194846558</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -576,12 +576,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>EDA_SCR_count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>EDA_SCR_count</t>
+          <t>EDA_Phasic_AUC</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -592,19 +592,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6516196770297616</v>
+        <v>0.6486114974313176</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9901884673684075</v>
+        <v>0.9871802877699635</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9942362770289704</v>
+        <v>0.9912280974305264</v>
       </c>
       <c r="D2" t="n">
-        <v>3519807.580580026</v>
+        <v>0.8472000266159746</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8502082062144186</v>
+        <v>0.8837154507133449</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -612,19 +612,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7018872323436988</v>
+        <v>0.6988790527452547</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6346941041233324</v>
+        <v>0.6316859245248884</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9621133156882345</v>
+        <v>0.9591051360897905</v>
       </c>
       <c r="D3" t="n">
-        <v>414666.5514846349</v>
+        <v>1.232970106078562</v>
       </c>
       <c r="E3" t="n">
-        <v>1.235978285677006</v>
+        <v>1.497733294676252</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
